--- a/Collections/EURO/Vatican_city/#EURO#Vatican_city#Commemorative#[2004-present]#UNC.xlsx
+++ b/Collections/EURO/Vatican_city/#EURO#Vatican_city#Commemorative#[2004-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Vatican_city\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B92E8E8-6C20-469A-8A7D-DC804DDEDC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA2EB2B-F855-4D05-9E7D-BD3C004FDADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="88">
   <si>
     <t>Year</t>
   </si>
@@ -338,6 +338,15 @@
   </si>
   <si>
     <t>500th centenary of the Swiss Pontifical Guard</t>
+  </si>
+  <si>
+    <t>76.000</t>
+  </si>
+  <si>
+    <t>550th Anniversary - Birth of Michelangelo</t>
+  </si>
+  <si>
+    <t>Holy Year</t>
   </si>
 </sst>
 </file>
@@ -797,7 +806,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1005,6 +1014,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,7 +1025,23 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1076,9 +1104,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1429,7 +1457,7 @@
         <v>76</v>
       </c>
       <c r="I3" s="7" t="str">
-        <f t="shared" ref="I3:I32" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I3:I33" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2199,24 +2227,81 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="35">
+        <v>2025</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="40">
+        <v>0</v>
+      </c>
       <c r="H33" s="66" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="34" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I33" s="73" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="46">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="50"/>
+      <c r="G34" s="51">
+        <v>0</v>
+      </c>
       <c r="H34" s="67"/>
     </row>
-    <row r="35" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="27"/>
+      <c r="G35" s="52">
+        <v>0</v>
+      </c>
       <c r="H35" s="67"/>
     </row>
-    <row r="36" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H36" s="67"/>
     </row>
-    <row r="37" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H37" s="67"/>
     </row>
-    <row r="38" spans="8:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H38" s="67"/>
     </row>
   </sheetData>
@@ -2227,11 +2312,28 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G3:G24 G27:G31">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G24 G27:G31">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2243,12 +2345,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
+  <conditionalFormatting sqref="G26">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2260,12 +2379,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
+  <conditionalFormatting sqref="G33">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
+  <conditionalFormatting sqref="G33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2277,12 +2396,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+  <conditionalFormatting sqref="G34:G35">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
+  <conditionalFormatting sqref="G34:G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
